--- a/SPEC MyBook Pro L7.xlsx
+++ b/SPEC MyBook Pro L7.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Downloads\Spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Desktop\axioo_b2g\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5C92C9-BC25-4F1C-A579-CDE8FBD5E70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152DC75A-9FE2-477D-8F7E-D6DEE7E0177D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,36 +60,6 @@
     <t>Intel® Core™  i7-1255U Processor (10 Cores, 12 Threads, TDP:15W)</t>
   </si>
   <si>
-    <r>
-      <t>Performance Cores:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 2 Cores, 4 Threads, 1.7 GHz Base, 4.7 GHz Turbo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Efficient Cores:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 8 Cores, 8 Threads, 1.2 GHz Base, 3.5 GHz Turbo</t>
-    </r>
-  </si>
-  <si>
     <t>Code Name</t>
   </si>
   <si>
@@ -833,12 +803,42 @@
   <si>
     <t>10. Video Setting</t>
   </si>
+  <si>
+    <r>
+      <t>Performance Cores:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2 Cores, 4 Threads, 1.7 GHz Base, 4.7 GHz Turbo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Efficient Cores:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 8 Cores, 8 Threads, 1.2 GHz Base, 3.5 GHz Turbo</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -913,11 +913,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
@@ -989,6 +984,54 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1287,49 +1330,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1343,11 +1357,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1355,40 +1364,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1412,7 +1400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1428,7 +1416,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1451,26 +1439,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="21" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1491,20 +1479,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="20" fontId="5" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="18" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="17" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
@@ -1516,10 +1504,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
@@ -1528,19 +1516,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -1552,31 +1540,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1590,7 +1578,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1599,9 +1587,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1629,6 +1614,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1638,49 +1632,122 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3456,366 +3523,364 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="148" customWidth="1"/>
-    <col min="2" max="2" width="88.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="74.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" style="160" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.6640625" style="117" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="8.88671875" style="117"/>
+    <col min="6" max="6" width="21.44140625" style="117" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.6640625" style="117" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" style="117"/>
+    <col min="10" max="10" width="21.44140625" style="117" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="74.6640625" style="117" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="117"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="121"/>
-      <c r="G1" s="28"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="119"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F2" s="121"/>
-      <c r="G2" s="20"/>
+      <c r="B2" s="116" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="118"/>
+      <c r="G2" s="120"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="138"/>
-      <c r="B3" s="27"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="20"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="120"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="121"/>
-      <c r="G4" s="20"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="120"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="140"/>
-      <c r="B5" s="23" t="s">
+      <c r="A5" s="125"/>
+      <c r="B5" s="126" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" s="127"/>
+      <c r="G5" s="119"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="128"/>
+      <c r="B6" s="129" t="s">
+        <v>243</v>
+      </c>
+      <c r="F6" s="127"/>
+      <c r="G6" s="119"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="28"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="141"/>
-      <c r="B6" s="24" t="s">
+      <c r="B7" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="28"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="10" t="s">
+      <c r="F7" s="131"/>
+      <c r="G7" s="132"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B8" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="31"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="10" t="s">
+      <c r="F8" s="134"/>
+      <c r="G8" s="135"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="136" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="111" t="s">
+      <c r="B9" s="137" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="33"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="11" t="s">
+      <c r="F9" s="138"/>
+      <c r="G9" s="122"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B10" s="140" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="27"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="142" t="s">
+      <c r="F10" s="127"/>
+      <c r="G10" s="119"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B11" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="28"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="10" t="s">
+      <c r="F11" s="127"/>
+      <c r="G11" s="119"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B12" s="130" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="29"/>
-      <c r="G11" s="28"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="10" t="s">
+      <c r="F12" s="127"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="130" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B13" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="29"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="10" t="s">
+      <c r="F13" s="118"/>
+      <c r="G13" s="119"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B14" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="121"/>
-      <c r="G13" s="28"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="143" t="s">
+      <c r="F14" s="118"/>
+      <c r="G14" s="142"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="141"/>
+      <c r="B15" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="F15" s="118"/>
+      <c r="G15" s="119"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="121"/>
-      <c r="G14" s="17"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="143"/>
-      <c r="B15" s="11" t="s">
+      <c r="B16" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="121"/>
-      <c r="G15" s="28"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="143" t="s">
+      <c r="F16" s="118"/>
+      <c r="G16" s="119"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="141"/>
+      <c r="B17" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="F17" s="118"/>
+      <c r="G17" s="119"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="141"/>
+      <c r="B18" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="121"/>
-      <c r="G16" s="28"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="143"/>
-      <c r="B17" s="10" t="s">
+      <c r="F18" s="118"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="141"/>
+      <c r="B19" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="121"/>
-      <c r="G17" s="28"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="143"/>
-      <c r="B18" s="10" t="s">
+      <c r="F19" s="118"/>
+      <c r="G19" s="144"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="141"/>
+      <c r="B20" s="143" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="121"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="143"/>
-      <c r="B19" s="12" t="s">
+      <c r="F20" s="118"/>
+      <c r="G20" s="119"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="141"/>
+      <c r="B21" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="121"/>
-      <c r="G19" s="34"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="143"/>
-      <c r="B20" s="12" t="s">
+      <c r="F21" s="118"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="141"/>
+      <c r="B22" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="121"/>
-      <c r="G20" s="28"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="143"/>
-      <c r="B21" s="15" t="s">
+      <c r="F22" s="118"/>
+      <c r="G22" s="119"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="141"/>
+      <c r="B23" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="121"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="143"/>
-      <c r="B22" s="15" t="s">
+      <c r="F23" s="118"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="121"/>
-      <c r="G22" s="28"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="143"/>
-      <c r="B23" s="10" t="s">
+      <c r="B24" s="130" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="121"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="139" t="s">
+      <c r="F24" s="118"/>
+      <c r="G24" s="122"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="128"/>
+      <c r="B25" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="F25" s="118"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="121"/>
-      <c r="G24" s="27"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="141"/>
-      <c r="B25" s="12" t="s">
+      <c r="B26" s="140" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="121"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="143" t="s">
+      <c r="F26" s="127"/>
+      <c r="G26" s="119"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="141"/>
+      <c r="B27" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="F27" s="118"/>
+      <c r="G27" s="119"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="28"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="143"/>
-      <c r="B27" s="12" t="s">
+      <c r="B28" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="121"/>
-      <c r="G27" s="28"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="143" t="s">
+      <c r="F28" s="118"/>
+      <c r="G28" s="119"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="141"/>
+      <c r="B29" s="146" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="F29" s="127"/>
+      <c r="G29" s="119"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="121"/>
-      <c r="G28" s="28"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="143"/>
-      <c r="B29" s="8" t="s">
+      <c r="B30" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="29"/>
-      <c r="G29" s="28"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="10" t="s">
+      <c r="F30" s="127"/>
+      <c r="G30" s="147"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B31" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="29"/>
-      <c r="G30" s="35"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="10" t="s">
+      <c r="F31" s="127"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B32" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="29"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="10" t="s">
+      <c r="F32" s="127"/>
+    </row>
+    <row r="33" spans="1:2" ht="13.2">
+      <c r="A33" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B33" s="149" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="29"/>
-    </row>
-    <row r="33" spans="1:2" ht="15">
-      <c r="A33" s="10" t="s">
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="130" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B34" s="150" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="144"/>
-      <c r="B35" s="2"/>
+      <c r="A35" s="151"/>
+      <c r="B35" s="152"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="144"/>
-      <c r="B36" s="2"/>
+      <c r="A36" s="151"/>
+      <c r="B36" s="152"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="145"/>
-      <c r="B37" s="17"/>
+      <c r="A37" s="153"/>
+      <c r="B37" s="142"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="145"/>
-      <c r="B38" s="17"/>
+      <c r="A38" s="153"/>
+      <c r="B38" s="142"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="138"/>
-      <c r="B39" s="4"/>
+      <c r="A39" s="121"/>
+      <c r="B39" s="154"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="144"/>
-      <c r="B40" s="5"/>
+      <c r="A40" s="151"/>
+      <c r="B40" s="155"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="144"/>
-      <c r="B41" s="1"/>
+      <c r="A41" s="151"/>
+      <c r="B41" s="156"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="144"/>
-      <c r="B42" s="1"/>
+      <c r="A42" s="151"/>
+      <c r="B42" s="156"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="144"/>
-      <c r="B43" s="1"/>
+      <c r="A43" s="151"/>
+      <c r="B43" s="156"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="146"/>
-      <c r="B44" s="6"/>
+      <c r="A44" s="157"/>
+      <c r="B44" s="158"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="147"/>
-      <c r="B45" s="5"/>
+      <c r="A45" s="159"/>
+      <c r="B45" s="155"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="F1:F4"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="F15:F21"/>
-    <mergeCell ref="F22:F23"/>
     <mergeCell ref="F27:F28"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A26:A27"/>
@@ -3823,6 +3888,11 @@
     <mergeCell ref="A16:A23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="F1:F4"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="F15:F21"/>
+    <mergeCell ref="F22:F23"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3843,1334 +3913,1334 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="C1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="15" thickBot="1"/>
     <row r="3" spans="2:6" ht="16.2" thickBot="1">
-      <c r="B3" s="125"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="131" t="s">
+      <c r="B3" s="103"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="109" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="110"/>
+      <c r="F3" s="111"/>
+    </row>
+    <row r="4" spans="2:6" ht="15" thickBot="1">
+      <c r="B4" s="105"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="113"/>
+      <c r="F4" s="114"/>
+    </row>
+    <row r="5" spans="2:6" ht="15" thickBot="1">
+      <c r="B5" s="105"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="132"/>
-      <c r="F3" s="133"/>
-    </row>
-    <row r="4" spans="2:6" ht="15" thickBot="1">
-      <c r="B4" s="127"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="134" t="s">
+      <c r="E5" s="113"/>
+      <c r="F5" s="114"/>
+    </row>
+    <row r="6" spans="2:6" ht="15" thickBot="1">
+      <c r="B6" s="107"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="112" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="113"/>
+      <c r="F6" s="114"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="135"/>
-      <c r="F4" s="136"/>
-    </row>
-    <row r="5" spans="2:6" ht="15" thickBot="1">
-      <c r="B5" s="127"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="134" t="s">
+    </row>
+    <row r="9" spans="2:6" ht="15" thickBot="1">
+      <c r="B9" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="135"/>
-      <c r="F5" s="136"/>
-    </row>
-    <row r="6" spans="2:6" ht="15" thickBot="1">
-      <c r="B6" s="129"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="134" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="135"/>
-      <c r="F6" s="136"/>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="36" t="s">
+      <c r="C9" s="27" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" ht="15" thickBot="1">
-      <c r="B9" s="48" t="s">
+      <c r="D9" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="E9" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="112" t="s">
+      <c r="F9" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="48" t="s">
+    </row>
+    <row r="10" spans="2:6" ht="15" thickTop="1">
+      <c r="B10" s="29">
+        <v>1</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="D10" s="30" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" ht="15" thickTop="1">
-      <c r="B10" s="50">
+      <c r="E10" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="30"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="20">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="20">
+        <v>3</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="20">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="80">
+        <v>57</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="20">
         <v>1</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C17" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="51"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="41">
+      <c r="F17" s="23"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="20">
         <v>2</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="41">
+      <c r="C18" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="24"/>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="20">
         <v>3</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="41">
+      <c r="C19" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="23"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="20">
         <v>4</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="101">
-        <v>57</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="38"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="39" t="s">
+      <c r="C20" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="23"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="26"/>
+      <c r="E21" s="12"/>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="2:6" ht="15" thickBot="1">
+      <c r="B23" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="15" thickTop="1">
+      <c r="B24" s="29">
+        <v>1</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="90" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="30"/>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="20">
+        <v>2</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="20">
+        <v>3</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="26"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="2:6" ht="15" thickBot="1">
+      <c r="B29" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="40" t="s">
+      <c r="E29" s="28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="15" thickTop="1">
+      <c r="B30" s="29">
+        <v>1</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="92">
+        <v>2</v>
+      </c>
+      <c r="C31" s="93" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="94" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="95"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="95"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="41">
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="35">
         <v>1</v>
       </c>
-      <c r="C17" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="44"/>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="41">
+      <c r="C36" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="35">
         <v>2</v>
       </c>
-      <c r="C18" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="45"/>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="41">
+      <c r="C37" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="8"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="35">
         <v>3</v>
       </c>
-      <c r="C19" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="44"/>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="41">
+      <c r="C38" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="39"/>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="35">
         <v>4</v>
       </c>
-      <c r="C20" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="44"/>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="47"/>
-      <c r="E21" s="26"/>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="2:6" ht="15" thickBot="1">
-      <c r="B23" s="48" t="s">
+      <c r="C39" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="35">
+        <v>5</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F40" s="39"/>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="35">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" s="39"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="35">
+        <v>7</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" s="39"/>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="35">
+        <v>8</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F43" s="39"/>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="35">
+        <v>9</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="39"/>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="35">
+        <v>10</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F45" s="8"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="35">
+        <v>11</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F46" s="39"/>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="35">
+        <v>12</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F47" s="5"/>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48" s="35">
+        <v>13</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F48" s="5"/>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="35">
+        <v>14</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F49" s="5"/>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="35">
+        <v>15</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F50" s="23"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="35">
+        <v>16</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="5"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="35">
+        <v>17</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" s="5"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="35">
+        <v>18</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" s="5"/>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54" s="35">
+        <v>19</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="5"/>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="41"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="41" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="15" thickBot="1">
+      <c r="B57" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D57" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="E57" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" ht="15" thickTop="1">
+      <c r="B58" s="29">
+        <v>1</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" s="42"/>
+      <c r="E58" s="43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="20">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" s="42"/>
+      <c r="E59" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60" s="29">
+        <v>3</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D60" s="42"/>
+      <c r="E60" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="29">
+        <v>4</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D61" s="42"/>
+      <c r="E61" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="44"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
+      <c r="E62" s="46"/>
+    </row>
+    <row r="63" spans="2:6">
+      <c r="B63" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="46"/>
+    </row>
+    <row r="64" spans="2:6" ht="15" thickBot="1">
+      <c r="B64" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="D64" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" ht="15.75" customHeight="1" thickTop="1">
+      <c r="B65" s="29">
+        <v>1</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="D65" s="99" t="s">
+        <v>140</v>
+      </c>
+      <c r="E65" s="43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" ht="15" customHeight="1">
+      <c r="B66" s="20">
+        <v>2</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="99" t="s">
+        <v>142</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="B67" s="26"/>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="B68" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D68" s="49"/>
+    </row>
+    <row r="69" spans="2:5" ht="15" thickBot="1">
+      <c r="B69" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E69" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="48" t="s">
+    </row>
+    <row r="70" spans="2:5" ht="15" thickTop="1">
+      <c r="B70" s="29">
+        <v>1</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="D70" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="E70" s="51" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5">
+      <c r="B71" s="20">
+        <v>2</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D71" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5">
+      <c r="B72" s="20">
+        <v>3</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D72" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="E72" s="51" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5">
+      <c r="B73" s="26"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="55"/>
+    </row>
+    <row r="74" spans="2:5">
+      <c r="B74" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" s="57"/>
+      <c r="D74" s="58"/>
+      <c r="E74" s="57"/>
+    </row>
+    <row r="75" spans="2:5" ht="15" thickBot="1">
+      <c r="B75" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="D75" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="60" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" ht="15" thickTop="1">
+      <c r="B76" s="62">
+        <v>1</v>
+      </c>
+      <c r="C76" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="D76" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="E76" s="62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5">
+      <c r="B77" s="64">
+        <v>2</v>
+      </c>
+      <c r="C77" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" s="64" t="s">
+        <v>160</v>
+      </c>
+      <c r="E77" s="62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5">
+      <c r="B78" s="20">
+        <v>3</v>
+      </c>
+      <c r="C78" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="D78" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="E78" s="62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5">
+      <c r="B79" s="26"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="67"/>
+    </row>
+    <row r="81" spans="2:5">
+      <c r="B81" s="15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" ht="15" thickBot="1">
+      <c r="B82" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="69" t="s">
+        <v>58</v>
+      </c>
+      <c r="E82" s="69" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" ht="15" thickTop="1">
+      <c r="B83" s="29">
+        <v>1</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D83" s="30"/>
+      <c r="E83" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5">
+      <c r="B84" s="29">
+        <v>2</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D84" s="5"/>
+      <c r="E84" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5">
+      <c r="B85" s="29">
+        <v>3</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5">
+      <c r="B86" s="29">
+        <v>4</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D86" s="5"/>
+      <c r="E86" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5">
+      <c r="B87" s="29">
+        <v>5</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D87" s="5"/>
+      <c r="E87" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5">
+      <c r="B88" s="29">
+        <v>6</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5">
+      <c r="B89" s="29">
+        <v>7</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D89" s="5"/>
+      <c r="E89" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5">
+      <c r="B90" s="29">
+        <v>8</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D90" s="5"/>
+      <c r="E90" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5">
+      <c r="B91" s="26"/>
+    </row>
+    <row r="92" spans="2:5">
+      <c r="B92" s="70" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" ht="15" thickBot="1">
+      <c r="B93" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C93" s="71" t="s">
+        <v>172</v>
+      </c>
+      <c r="D93" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="E93" s="71" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" ht="15" thickTop="1">
+      <c r="B94" s="29">
+        <v>1</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="D94" s="98" t="s">
+        <v>174</v>
+      </c>
+      <c r="E94" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5">
+      <c r="B95" s="29">
+        <v>2</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E95" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5">
+      <c r="B96" s="29">
+        <v>3</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E96" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5">
+      <c r="B97" s="26"/>
+    </row>
+    <row r="98" spans="2:5">
+      <c r="B98" s="56" t="s">
+        <v>179</v>
+      </c>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="67"/>
+    </row>
+    <row r="99" spans="2:5" ht="15" thickBot="1">
+      <c r="B99" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="D99" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E99" s="59" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" ht="15" thickTop="1">
+      <c r="B100" s="62">
+        <v>1</v>
+      </c>
+      <c r="C100" s="100" t="s">
+        <v>183</v>
+      </c>
+      <c r="D100" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5">
+      <c r="B101" s="64">
+        <v>2</v>
+      </c>
+      <c r="C101" s="101"/>
+      <c r="D101" s="74" t="s">
+        <v>186</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5">
+      <c r="B102" s="64">
+        <v>3</v>
+      </c>
+      <c r="C102" s="101"/>
+      <c r="D102" s="74" t="s">
+        <v>188</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5">
+      <c r="B103" s="64">
+        <v>4</v>
+      </c>
+      <c r="C103" s="102"/>
+      <c r="D103" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="E103" s="20" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5">
+      <c r="B104" s="67"/>
+      <c r="C104" s="57"/>
+      <c r="D104" s="57"/>
+      <c r="E104" s="67"/>
+    </row>
+    <row r="105" spans="2:5">
+      <c r="B105" s="75" t="s">
+        <v>179</v>
+      </c>
+      <c r="C105" s="57"/>
+      <c r="D105" s="57"/>
+      <c r="E105" s="67"/>
+    </row>
+    <row r="106" spans="2:5" ht="15" thickBot="1">
+      <c r="B106" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="D106" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E106" s="59" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" ht="15" thickTop="1">
+      <c r="B107" s="62">
+        <v>1</v>
+      </c>
+      <c r="C107" s="73" t="s">
+        <v>193</v>
+      </c>
+      <c r="D107" s="73" t="s">
+        <v>194</v>
+      </c>
+      <c r="E107" s="62" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5">
+      <c r="B108" s="62">
+        <v>2</v>
+      </c>
+      <c r="C108" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="D108" s="74"/>
+      <c r="E108" s="76" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5">
+      <c r="B109" s="62">
+        <v>3</v>
+      </c>
+      <c r="C109" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="D109" s="74"/>
+      <c r="E109" s="76" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5">
+      <c r="B110" s="67"/>
+      <c r="C110" s="57"/>
+      <c r="D110" s="57"/>
+      <c r="E110" s="77"/>
+    </row>
+    <row r="111" spans="2:5">
+      <c r="B111" s="56" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" ht="15" thickTop="1">
-      <c r="B24" s="50">
+      <c r="C111" s="57"/>
+      <c r="D111" s="57"/>
+      <c r="E111" s="67"/>
+    </row>
+    <row r="112" spans="2:5" ht="15" thickBot="1">
+      <c r="B112" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="C112" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="D112" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112" s="59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" ht="15" thickTop="1">
+      <c r="B113" s="62">
         <v>1</v>
       </c>
-      <c r="C24" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="111" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="51"/>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="41">
+      <c r="C113" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="D113" s="73" t="s">
+        <v>200</v>
+      </c>
+      <c r="E113" s="62" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5">
+      <c r="B114" s="62">
         <v>2</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="41">
-        <v>3</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" s="47"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="2:6" ht="15" thickBot="1">
-      <c r="B29" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="E29" s="49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" ht="15" thickTop="1">
-      <c r="B30" s="50">
-        <v>1</v>
-      </c>
-      <c r="C30" s="55" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="E30" s="56" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="113">
-        <v>2</v>
-      </c>
-      <c r="C31" s="114" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="114" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" s="115" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="116"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="116"/>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="F35" s="58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="56">
-        <v>1</v>
-      </c>
-      <c r="C36" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" s="18"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="56">
-        <v>2</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" s="19"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="56">
-        <v>3</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" s="60"/>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="56">
-        <v>4</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F39" s="60"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="56">
-        <v>5</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="F40" s="60"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="56">
-        <v>6</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F41" s="60"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="56">
-        <v>7</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F42" s="60"/>
-    </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="56">
-        <v>8</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F43" s="60"/>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="56">
-        <v>9</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F44" s="60"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="56">
-        <v>10</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F45" s="19"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="56">
-        <v>11</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46" s="60"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="56">
-        <v>12</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" s="12"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="56">
-        <v>13</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" s="61" t="s">
-        <v>120</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F48" s="12"/>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="56">
-        <v>14</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F49" s="12"/>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="56">
-        <v>15</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F50" s="44"/>
-    </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="56">
-        <v>16</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F51" s="12"/>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="56">
-        <v>17</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F52" s="12"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="56">
-        <v>18</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F53" s="12"/>
-    </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="56">
-        <v>19</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F54" s="12"/>
-    </row>
-    <row r="55" spans="2:6">
-      <c r="B55" s="62"/>
-    </row>
-    <row r="56" spans="2:6">
-      <c r="B56" s="62" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" ht="15" thickBot="1">
-      <c r="B57" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="D57" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="E57" s="48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" ht="15" thickTop="1">
-      <c r="B58" s="50">
-        <v>1</v>
-      </c>
-      <c r="C58" s="55" t="s">
-        <v>135</v>
-      </c>
-      <c r="D58" s="63"/>
-      <c r="E58" s="64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="41">
-        <v>2</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="63"/>
-      <c r="E59" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6">
-      <c r="B60" s="50">
-        <v>3</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="63"/>
-      <c r="E60" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="50">
-        <v>4</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" s="63"/>
-      <c r="E61" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6">
-      <c r="B62" s="65"/>
-      <c r="C62" s="66"/>
-      <c r="D62" s="66"/>
-      <c r="E62" s="67"/>
-    </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="C63" s="66"/>
-      <c r="D63" s="66"/>
-      <c r="E63" s="67"/>
-    </row>
-    <row r="64" spans="2:6" ht="15" thickBot="1">
-      <c r="B64" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="C64" s="69" t="s">
-        <v>140</v>
-      </c>
-      <c r="D64" s="118" t="s">
-        <v>60</v>
-      </c>
-      <c r="E64" s="69" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" ht="15.75" customHeight="1" thickTop="1">
-      <c r="B65" s="50">
-        <v>1</v>
-      </c>
-      <c r="C65" s="55" t="s">
-        <v>141</v>
-      </c>
-      <c r="D65" s="120" t="s">
-        <v>142</v>
-      </c>
-      <c r="E65" s="64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" ht="15" customHeight="1">
-      <c r="B66" s="41">
-        <v>2</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D66" s="120" t="s">
-        <v>144</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5">
-      <c r="B67" s="47"/>
-    </row>
-    <row r="68" spans="2:5">
-      <c r="B68" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="D68" s="70"/>
-    </row>
-    <row r="69" spans="2:5" ht="15" thickBot="1">
-      <c r="B69" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C69" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="D69" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="E69" s="48" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" ht="15" thickTop="1">
-      <c r="B70" s="50">
-        <v>1</v>
-      </c>
-      <c r="C70" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="D70" s="71" t="s">
-        <v>149</v>
-      </c>
-      <c r="E70" s="72" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5">
-      <c r="B71" s="41">
-        <v>2</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D71" s="73" t="s">
-        <v>152</v>
-      </c>
-      <c r="E71" s="72" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5">
-      <c r="B72" s="41">
-        <v>3</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D72" s="74" t="s">
-        <v>155</v>
-      </c>
-      <c r="E72" s="72" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5">
-      <c r="B73" s="47"/>
-      <c r="D73" s="75"/>
-      <c r="E73" s="76"/>
-    </row>
-    <row r="74" spans="2:5">
-      <c r="B74" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="C74" s="78"/>
-      <c r="D74" s="79"/>
-      <c r="E74" s="78"/>
-    </row>
-    <row r="75" spans="2:5" ht="15" thickBot="1">
-      <c r="B75" s="80" t="s">
-        <v>58</v>
-      </c>
-      <c r="C75" s="81" t="s">
-        <v>158</v>
-      </c>
-      <c r="D75" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="E75" s="81" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" ht="15" thickTop="1">
-      <c r="B76" s="83">
-        <v>1</v>
-      </c>
-      <c r="C76" s="84" t="s">
-        <v>159</v>
-      </c>
-      <c r="D76" s="85" t="s">
-        <v>160</v>
-      </c>
-      <c r="E76" s="83" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5">
-      <c r="B77" s="85">
-        <v>2</v>
-      </c>
-      <c r="C77" s="86" t="s">
-        <v>161</v>
-      </c>
-      <c r="D77" s="85" t="s">
-        <v>162</v>
-      </c>
-      <c r="E77" s="83" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5">
-      <c r="B78" s="41">
-        <v>3</v>
-      </c>
-      <c r="C78" s="86" t="s">
-        <v>163</v>
-      </c>
-      <c r="D78" s="85" t="s">
-        <v>164</v>
-      </c>
-      <c r="E78" s="83" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5">
-      <c r="B79" s="47"/>
-      <c r="C79" s="87"/>
-      <c r="D79" s="88"/>
-      <c r="E79" s="88"/>
-    </row>
-    <row r="81" spans="2:5">
-      <c r="B81" s="36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" ht="15" thickBot="1">
-      <c r="B82" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C82" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="D82" s="90" t="s">
-        <v>60</v>
-      </c>
-      <c r="E82" s="90" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" ht="15" thickTop="1">
-      <c r="B83" s="50">
-        <v>1</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D83" s="51"/>
-      <c r="E83" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5">
-      <c r="B84" s="50">
-        <v>2</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D84" s="12"/>
-      <c r="E84" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5">
-      <c r="B85" s="50">
-        <v>3</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E85" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5">
-      <c r="B86" s="50">
-        <v>4</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D86" s="12"/>
-      <c r="E86" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5">
-      <c r="B87" s="50">
-        <v>5</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="D87" s="12"/>
-      <c r="E87" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5">
-      <c r="B88" s="50">
-        <v>6</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D88" s="12"/>
-      <c r="E88" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5">
-      <c r="B89" s="50">
-        <v>7</v>
-      </c>
-      <c r="C89" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D89" s="12"/>
-      <c r="E89" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5">
-      <c r="B90" s="50">
-        <v>8</v>
-      </c>
-      <c r="C90" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5">
-      <c r="B91" s="47"/>
-    </row>
-    <row r="92" spans="2:5">
-      <c r="B92" s="91" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" ht="15" thickBot="1">
-      <c r="B93" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C93" s="92" t="s">
-        <v>174</v>
-      </c>
-      <c r="D93" s="92" t="s">
-        <v>60</v>
-      </c>
-      <c r="E93" s="92" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" ht="15" thickTop="1">
-      <c r="B94" s="50">
-        <v>1</v>
-      </c>
-      <c r="C94" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="D94" s="119" t="s">
-        <v>176</v>
-      </c>
-      <c r="E94" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5">
-      <c r="B95" s="50">
-        <v>2</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E95" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5">
-      <c r="B96" s="50">
-        <v>3</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E96" s="50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5">
-      <c r="B97" s="47"/>
-    </row>
-    <row r="98" spans="2:5">
-      <c r="B98" s="77" t="s">
-        <v>181</v>
-      </c>
-      <c r="C98" s="78"/>
-      <c r="D98" s="78"/>
-      <c r="E98" s="88"/>
-    </row>
-    <row r="99" spans="2:5" ht="15" thickBot="1">
-      <c r="B99" s="80" t="s">
-        <v>182</v>
-      </c>
-      <c r="C99" s="93" t="s">
-        <v>183</v>
-      </c>
-      <c r="D99" s="80" t="s">
-        <v>60</v>
-      </c>
-      <c r="E99" s="80" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" ht="15" thickTop="1">
-      <c r="B100" s="83">
-        <v>1</v>
-      </c>
-      <c r="C100" s="122" t="s">
-        <v>185</v>
-      </c>
-      <c r="D100" s="94" t="s">
-        <v>186</v>
-      </c>
-      <c r="E100" s="41" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5">
-      <c r="B101" s="85">
-        <v>2</v>
-      </c>
-      <c r="C101" s="123"/>
-      <c r="D101" s="95" t="s">
-        <v>188</v>
-      </c>
-      <c r="E101" s="41" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5">
-      <c r="B102" s="85">
-        <v>3</v>
-      </c>
-      <c r="C102" s="123"/>
-      <c r="D102" s="95" t="s">
-        <v>190</v>
-      </c>
-      <c r="E102" s="41" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="103" spans="2:5">
-      <c r="B103" s="85">
-        <v>4</v>
-      </c>
-      <c r="C103" s="124"/>
-      <c r="D103" s="95" t="s">
-        <v>192</v>
-      </c>
-      <c r="E103" s="41" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="104" spans="2:5">
-      <c r="B104" s="88"/>
-      <c r="C104" s="78"/>
-      <c r="D104" s="78"/>
-      <c r="E104" s="88"/>
-    </row>
-    <row r="105" spans="2:5">
-      <c r="B105" s="96" t="s">
-        <v>181</v>
-      </c>
-      <c r="C105" s="78"/>
-      <c r="D105" s="78"/>
-      <c r="E105" s="88"/>
-    </row>
-    <row r="106" spans="2:5" ht="15" thickBot="1">
-      <c r="B106" s="80" t="s">
-        <v>182</v>
-      </c>
-      <c r="C106" s="80" t="s">
-        <v>183</v>
-      </c>
-      <c r="D106" s="80" t="s">
-        <v>60</v>
-      </c>
-      <c r="E106" s="80" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="107" spans="2:5" ht="15" thickTop="1">
-      <c r="B107" s="83">
-        <v>1</v>
-      </c>
-      <c r="C107" s="94" t="s">
-        <v>195</v>
-      </c>
-      <c r="D107" s="94" t="s">
-        <v>196</v>
-      </c>
-      <c r="E107" s="83" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="108" spans="2:5">
-      <c r="B108" s="83">
-        <v>2</v>
-      </c>
-      <c r="C108" s="95" t="s">
-        <v>198</v>
-      </c>
-      <c r="D108" s="95"/>
-      <c r="E108" s="97" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="109" spans="2:5">
-      <c r="B109" s="83">
-        <v>3</v>
-      </c>
-      <c r="C109" s="95" t="s">
-        <v>200</v>
-      </c>
-      <c r="D109" s="95"/>
-      <c r="E109" s="97" t="s">
+      <c r="C114" s="74" t="s">
+        <v>202</v>
+      </c>
+      <c r="D114" s="74" t="s">
+        <v>203</v>
+      </c>
+      <c r="E114" s="62" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="110" spans="2:5">
-      <c r="B110" s="88"/>
-      <c r="C110" s="78"/>
-      <c r="D110" s="78"/>
-      <c r="E110" s="98"/>
-    </row>
-    <row r="111" spans="2:5">
-      <c r="B111" s="77" t="s">
-        <v>86</v>
-      </c>
-      <c r="C111" s="78"/>
-      <c r="D111" s="78"/>
-      <c r="E111" s="88"/>
-    </row>
-    <row r="112" spans="2:5" ht="15" thickBot="1">
-      <c r="B112" s="80" t="s">
-        <v>182</v>
-      </c>
-      <c r="C112" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="D112" s="80" t="s">
-        <v>60</v>
-      </c>
-      <c r="E112" s="80" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="113" spans="2:5" ht="15" thickTop="1">
-      <c r="B113" s="83">
-        <v>1</v>
-      </c>
-      <c r="C113" s="94" t="s">
-        <v>43</v>
-      </c>
-      <c r="D113" s="94" t="s">
-        <v>202</v>
-      </c>
-      <c r="E113" s="83" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="114" spans="2:5">
-      <c r="B114" s="83">
-        <v>2</v>
-      </c>
-      <c r="C114" s="95" t="s">
+    <row r="116" spans="2:5">
+      <c r="B116" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="D114" s="95" t="s">
+      <c r="E116" s="78" t="s">
         <v>205</v>
       </c>
-      <c r="E114" s="83" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="116" spans="2:5">
-      <c r="B116" s="99" t="s">
+    </row>
+    <row r="117" spans="2:5">
+      <c r="B117" s="78"/>
+      <c r="E117" s="78"/>
+    </row>
+    <row r="118" spans="2:5">
+      <c r="B118" s="78"/>
+      <c r="E118" s="78"/>
+    </row>
+    <row r="119" spans="2:5">
+      <c r="B119" s="78"/>
+      <c r="E119" s="78"/>
+    </row>
+    <row r="120" spans="2:5">
+      <c r="B120" s="78"/>
+      <c r="E120" s="78"/>
+    </row>
+    <row r="121" spans="2:5">
+      <c r="B121" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="E116" s="99" t="s">
+      <c r="E121" s="79" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5">
+      <c r="B122" s="78" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="117" spans="2:5">
-      <c r="B117" s="99"/>
-      <c r="E117" s="99"/>
-    </row>
-    <row r="118" spans="2:5">
-      <c r="B118" s="99"/>
-      <c r="E118" s="99"/>
-    </row>
-    <row r="119" spans="2:5">
-      <c r="B119" s="99"/>
-      <c r="E119" s="99"/>
-    </row>
-    <row r="120" spans="2:5">
-      <c r="B120" s="99"/>
-      <c r="E120" s="99"/>
-    </row>
-    <row r="121" spans="2:5">
-      <c r="B121" s="100" t="s">
+      <c r="E122" s="78" t="s">
         <v>208</v>
-      </c>
-      <c r="E121" s="100" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="122" spans="2:5">
-      <c r="B122" s="99" t="s">
-        <v>209</v>
-      </c>
-      <c r="E122" s="99" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -5197,88 +5267,88 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2" spans="1:24" ht="18">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="81" t="s">
+        <v>209</v>
+      </c>
+      <c r="K2" s="81" t="s">
+        <v>210</v>
+      </c>
+      <c r="N2" s="82"/>
+      <c r="X2" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="K2" s="102" t="s">
-        <v>212</v>
-      </c>
-      <c r="N2" s="103"/>
-      <c r="X2" s="20" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="18" spans="4:14">
       <c r="G18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="4:14">
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
     </row>
     <row r="25" spans="4:14" ht="18">
-      <c r="I25" s="102" t="s">
-        <v>214</v>
+      <c r="I25" s="81" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="4:14">
       <c r="K27" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="4:14">
+      <c r="D29" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="55" spans="4:13">
+      <c r="D55" s="9" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="29" spans="4:14">
-      <c r="D29" s="20" t="s">
+      <c r="M55" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="77" spans="4:13">
+      <c r="D77" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="M29" s="20" t="s">
+      <c r="M77" s="9" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="55" spans="4:13">
-      <c r="D55" s="20" t="s">
+    <row r="102" spans="5:15" ht="18">
+      <c r="I102" s="81" t="s">
         <v>217</v>
-      </c>
-      <c r="M55" s="20" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="77" spans="4:13">
-      <c r="D77" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="M77" s="20" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="102" spans="5:15" ht="18">
-      <c r="I102" s="102" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="104" spans="5:15">
       <c r="O104" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="106" spans="5:15">
+      <c r="E106" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="129" spans="5:5">
+      <c r="E129" s="9" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="106" spans="5:15">
-      <c r="E106" s="20" t="s">
+    <row r="152" spans="9:12" ht="18">
+      <c r="I152" s="81" t="s">
         <v>221</v>
-      </c>
-    </row>
-    <row r="129" spans="5:5">
-      <c r="E129" s="20" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="152" spans="9:12" ht="18">
-      <c r="I152" s="102" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="154" spans="9:12">
       <c r="L154" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -5299,129 +5369,129 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11">
-      <c r="B2" s="104" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="103"/>
+      <c r="B2" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="83"/>
+      <c r="D2" s="82"/>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="108" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="108" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="108" t="s">
+      <c r="B3" s="87" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="87" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="87" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="87" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" s="68">
+        <v>1</v>
+      </c>
+      <c r="C4" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="50">
+        <v>0.41425925925925927</v>
+      </c>
+      <c r="E4" s="51" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" s="39">
+        <v>2</v>
+      </c>
+      <c r="C5" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="108" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" s="89">
-        <v>1</v>
-      </c>
-      <c r="C4" s="89" t="s">
+      <c r="D5" s="52">
+        <v>7.9571759259259259E-2</v>
+      </c>
+      <c r="E5" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" s="39">
+        <v>3</v>
+      </c>
+      <c r="C6" s="39" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="71">
-        <v>0.41425925925925927</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" s="60">
-        <v>2</v>
-      </c>
-      <c r="C5" s="60" t="s">
+      <c r="D6" s="53">
+        <v>9.7939814814814827E-2</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" s="39">
+        <v>4</v>
+      </c>
+      <c r="C7" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="D5" s="73">
-        <v>7.9571759259259259E-2</v>
-      </c>
-      <c r="E5" s="72" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" s="60">
-        <v>3</v>
-      </c>
-      <c r="C6" s="60" t="s">
+      <c r="D7" s="53">
+        <v>0.17916666666666667</v>
+      </c>
+      <c r="E7" s="51" t="s">
         <v>228</v>
       </c>
-      <c r="D6" s="74">
-        <v>9.7939814814814827E-2</v>
-      </c>
-      <c r="E6" s="72" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" s="60">
-        <v>4</v>
-      </c>
-      <c r="C7" s="60" t="s">
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="55"/>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="D9" s="13"/>
+      <c r="E9" s="55"/>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="55"/>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="55"/>
+    </row>
+    <row r="12" spans="2:11" ht="18">
+      <c r="B12" s="81" t="s">
         <v>229</v>
       </c>
-      <c r="D7" s="74">
-        <v>0.17916666666666667</v>
-      </c>
-      <c r="E7" s="72" t="s">
+      <c r="C12" s="88"/>
+      <c r="G12" s="81" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="76"/>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="D9" s="27"/>
-      <c r="E9" s="76"/>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="76"/>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="76"/>
-    </row>
-    <row r="12" spans="2:11" ht="18">
-      <c r="B12" s="102" t="s">
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" s="85"/>
+    </row>
+    <row r="37" spans="2:11" ht="18">
+      <c r="B37" s="89" t="s">
         <v>231</v>
       </c>
-      <c r="C12" s="109"/>
-      <c r="G12" s="102" t="s">
-        <v>232</v>
-      </c>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13" s="106"/>
-    </row>
-    <row r="37" spans="2:11" ht="18">
-      <c r="B37" s="110" t="s">
-        <v>233</v>
-      </c>
     </row>
     <row r="44" spans="2:11">
-      <c r="C44" s="104"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="104"/>
-      <c r="K44" s="104"/>
+      <c r="C44" s="83"/>
+      <c r="I44" s="83"/>
+      <c r="J44" s="83"/>
+      <c r="K44" s="83"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5435,68 +5505,68 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2" spans="2:20" ht="18">
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="81" t="s">
+        <v>232</v>
+      </c>
+      <c r="I2" s="81" t="s">
+        <v>233</v>
+      </c>
+      <c r="O2" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="I2" s="102" t="s">
+    </row>
+    <row r="3" spans="2:20">
+      <c r="B3" s="84"/>
+      <c r="J3" s="85"/>
+    </row>
+    <row r="4" spans="2:20">
+      <c r="T4" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="O2" s="102" t="s">
+    </row>
+    <row r="24" spans="2:16">
+      <c r="B24" s="84"/>
+      <c r="J24" s="84"/>
+    </row>
+    <row r="26" spans="2:16" ht="18">
+      <c r="C26" s="81" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="3" spans="2:20">
-      <c r="B3" s="105"/>
-      <c r="J3" s="106"/>
-    </row>
-    <row r="4" spans="2:20">
-      <c r="T4" s="20" t="s">
+      <c r="L26" s="81"/>
+    </row>
+    <row r="30" spans="2:16">
+      <c r="P30" s="84"/>
+    </row>
+    <row r="31" spans="2:16" ht="15.6">
+      <c r="P31" s="86"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="84"/>
+    </row>
+    <row r="51" spans="3:12" ht="18">
+      <c r="C51" s="81" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="2:16">
-      <c r="B24" s="105"/>
-      <c r="J24" s="105"/>
-    </row>
-    <row r="26" spans="2:16" ht="18">
-      <c r="C26" s="102" t="s">
+    <row r="52" spans="3:12" ht="18">
+      <c r="L52" s="81" t="s">
         <v>238</v>
       </c>
-      <c r="L26" s="102"/>
-    </row>
-    <row r="30" spans="2:16">
-      <c r="P30" s="105"/>
-    </row>
-    <row r="31" spans="2:16" ht="15.6">
-      <c r="P31" s="107"/>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="105"/>
-    </row>
-    <row r="51" spans="3:12" ht="18">
-      <c r="C51" s="102" t="s">
+    </row>
+    <row r="55" spans="3:12">
+      <c r="J55" s="84"/>
+    </row>
+    <row r="76" spans="8:8" ht="18">
+      <c r="H76" s="81" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="52" spans="3:12" ht="18">
-      <c r="L52" s="102" t="s">
+    <row r="88" spans="3:11" ht="18">
+      <c r="C88" s="81" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="55" spans="3:12">
-      <c r="J55" s="105"/>
-    </row>
-    <row r="76" spans="8:8" ht="18">
-      <c r="H76" s="102" t="s">
+      <c r="K88" s="81" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="88" spans="3:11" ht="18">
-      <c r="C88" s="102" t="s">
-        <v>242</v>
-      </c>
-      <c r="K88" s="102" t="s">
-        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -5507,12 +5577,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5751,20 +5823,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFD7CE84-2D8A-4763-98FE-D132BD52AA9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B71228ED-3B47-481D-9B3C-4B0F46A94ACC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
+    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5789,12 +5862,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B71228ED-3B47-481D-9B3C-4B0F46A94ACC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFD7CE84-2D8A-4763-98FE-D132BD52AA9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
-    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>